--- a/electivas/BOLSA DE ELECTIVAS.xlsx
+++ b/electivas/BOLSA DE ELECTIVAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniandes.sharepoint.com/sites/CoordinacionIELE/Documentos compartidos/Planeacion semestral/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Documents\pensum-interactivo\electivas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C6C249D-8366-475B-B6A6-C655B231B207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44857944-0AC2-4EEC-9E4D-818ABBE22999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ELECTIVAS IEE" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="90">
   <si>
     <t>PARA PENSUM DESDE 2024-I  (Vale por...)</t>
   </si>
@@ -303,13 +303,19 @@
   </si>
   <si>
     <t>PROFUNDIZACIÓN MICROELECTRONICA/INTELIGENCIA ARTIFICIAL</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>ES CURSO INTEGRADOR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
@@ -329,20 +335,29 @@
       <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
@@ -1036,7 +1051,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1079,9 +1094,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1293,6 +1305,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -1308,9 +1323,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1646,55 +1662,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD30170E-E355-43E6-8454-CC0CAF8DD44B}">
   <dimension ref="A1:M78"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="50.85546875" customWidth="1"/>
     <col min="4" max="4" width="48.7109375" customWidth="1"/>
     <col min="5" max="5" width="45.7109375" customWidth="1"/>
     <col min="6" max="6" width="45.5703125" customWidth="1"/>
-    <col min="7" max="7" width="52.5703125" style="46" customWidth="1"/>
-    <col min="8" max="13" width="9.140625" style="46"/>
+    <col min="7" max="7" width="52.5703125" style="45" customWidth="1"/>
+    <col min="8" max="13" width="9.140625" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="C1" s="123" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="124"/>
-      <c r="E1" s="125" t="s">
+    <row r="1" spans="1:8" ht="15.75" thickBot="1">
+      <c r="C1" s="122" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="123"/>
+      <c r="E1" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="126"/>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="F1" s="125"/>
+      <c r="G1" s="124" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="125"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" thickBot="1">
       <c r="B2" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="108" t="s">
+      <c r="D2" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="127" t="s">
+      <c r="F2" s="139" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A3" s="126" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="29" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="109" t="s">
+      <c r="D3" s="108" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="13" t="s">
@@ -1703,16 +1726,19 @@
       <c r="F3" s="12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="128"/>
-      <c r="B4" s="31" t="s">
+      <c r="G3" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A4" s="127"/>
+      <c r="B4" s="30" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="110" t="s">
+      <c r="D4" s="109" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -1721,16 +1747,19 @@
       <c r="F4" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="128"/>
-      <c r="B5" s="32" t="s">
+      <c r="G4" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A5" s="127"/>
+      <c r="B5" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="110" t="s">
+      <c r="D5" s="109" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -1739,16 +1768,19 @@
       <c r="F5" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="128"/>
-      <c r="B6" s="32" t="s">
+      <c r="G5" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A6" s="127"/>
+      <c r="B6" s="31" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="111" t="s">
+      <c r="D6" s="110" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -1757,16 +1789,19 @@
       <c r="F6" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="128"/>
-      <c r="B7" s="32" t="s">
+      <c r="G6" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A7" s="127"/>
+      <c r="B7" s="31" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="111" t="s">
+      <c r="D7" s="110" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -1775,32 +1810,38 @@
       <c r="F7" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="128"/>
-      <c r="B8" s="32" t="s">
+      <c r="G7" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A8" s="127"/>
+      <c r="B8" s="31" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="110" t="s">
+      <c r="D8" s="109" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="105" t="s">
+      <c r="F8" s="104" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="128"/>
-      <c r="B9" s="32" t="s">
+      <c r="G8" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A9" s="127"/>
+      <c r="B9" s="31" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="110" t="s">
+      <c r="D9" s="109" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -1809,16 +1850,19 @@
       <c r="F9" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="128"/>
-      <c r="B10" s="32" t="s">
+      <c r="G9" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A10" s="127"/>
+      <c r="B10" s="31" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="110" t="s">
+      <c r="D10" s="109" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -1827,216 +1871,253 @@
       <c r="F10" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="128"/>
-      <c r="B11" s="32" t="s">
+      <c r="G10" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A11" s="127"/>
+      <c r="B11" s="31" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="110" t="s">
+      <c r="D11" s="109" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="105" t="s">
+      <c r="F11" s="104" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="128"/>
-      <c r="B12" s="51" t="s">
+      <c r="G11" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A12" s="127"/>
+      <c r="B12" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="112" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="105" t="s">
+      <c r="C12" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="111" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="104" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="128"/>
-      <c r="B13" s="33" t="s">
+      <c r="G12" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A13" s="127"/>
+      <c r="B13" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="112" t="s">
+      <c r="D13" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="128"/>
-      <c r="B14" s="47" t="s">
+      <c r="E13" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A14" s="127"/>
+      <c r="B14" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="113" t="s">
+      <c r="D14" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="40" t="s">
+      <c r="E14" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="39" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="128"/>
-      <c r="B15" s="48" t="s">
+      <c r="G14" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A15" s="127"/>
+      <c r="B15" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="43" t="s">
+      <c r="C15" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="114" t="s">
+      <c r="D15" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="43" t="s">
+      <c r="E15" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="42" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="128"/>
-      <c r="B16" s="48" t="s">
+      <c r="F15" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A16" s="127"/>
+      <c r="B16" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="43" t="s">
+      <c r="C16" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="114" t="s">
+      <c r="D16" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="42" t="s">
+      <c r="E16" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="41" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="128"/>
-      <c r="B17" s="49" t="s">
+      <c r="G16" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A17" s="127"/>
+      <c r="B17" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="43" t="s">
+      <c r="C17" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="114" t="s">
+      <c r="D17" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="43" t="s">
+      <c r="E17" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="42" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="128"/>
-      <c r="B18" s="49" t="s">
+      <c r="F17" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A18" s="127"/>
+      <c r="B18" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="43" t="s">
+      <c r="C18" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="114" t="s">
+      <c r="D18" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="43" t="s">
+      <c r="E18" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="42" t="s">
+      <c r="F18" s="41" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="128"/>
-      <c r="B19" s="49" t="s">
+      <c r="G18" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A19" s="127"/>
+      <c r="B19" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="43" t="s">
+      <c r="C19" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="115" t="s">
+      <c r="D19" s="114" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="106" t="s">
+      <c r="E19" s="105" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="42" t="s">
+      <c r="F19" s="41" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="129" t="s">
+      <c r="G19" s="12">
+        <v>1</v>
+      </c>
+      <c r="J19" s="140"/>
+    </row>
+    <row r="20" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A20" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="50" t="s">
+      <c r="B20" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="45" t="s">
+      <c r="C20" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="116" t="s">
+      <c r="D20" s="115" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="45" t="s">
+      <c r="E20" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="44" t="s">
+      <c r="F20" s="43" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="130"/>
-      <c r="B21" s="34" t="s">
+      <c r="G20" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A21" s="129"/>
+      <c r="B21" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="117" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="22" t="s">
+      <c r="C21" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="116" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="21" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="130"/>
-      <c r="B22" s="35" t="s">
+      <c r="G21" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A22" s="129"/>
+      <c r="B22" s="34" t="s">
         <v>37</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="118" t="s">
+      <c r="D22" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="7" t="s">
@@ -2045,34 +2126,40 @@
       <c r="F22" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="130"/>
-      <c r="B23" s="35" t="s">
+      <c r="G22" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A23" s="129"/>
+      <c r="B23" s="34" t="s">
         <v>38</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="119" t="s">
+      <c r="D23" s="118" t="s">
         <v>39</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="107" t="s">
+      <c r="F23" s="106" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="130"/>
-      <c r="B24" s="35" t="s">
+      <c r="G23" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A24" s="129"/>
+      <c r="B24" s="34" t="s">
         <v>40</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="118" t="s">
+      <c r="D24" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E24" s="7" t="s">
@@ -2081,16 +2168,19 @@
       <c r="F24" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="130"/>
-      <c r="B25" s="35" t="s">
+      <c r="G24" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A25" s="129"/>
+      <c r="B25" s="34" t="s">
         <v>41</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="118" t="s">
+      <c r="D25" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="7" t="s">
@@ -2099,16 +2189,19 @@
       <c r="F25" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="130"/>
-      <c r="B26" s="36" t="s">
+      <c r="G25" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A26" s="129"/>
+      <c r="B26" s="35" t="s">
         <v>42</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="118" t="s">
+      <c r="D26" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="7" t="s">
@@ -2117,16 +2210,19 @@
       <c r="F26" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="130"/>
-      <c r="B27" s="36" t="s">
+      <c r="G26" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A27" s="129"/>
+      <c r="B27" s="35" t="s">
         <v>43</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="118" t="s">
+      <c r="D27" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="7" t="s">
@@ -2135,16 +2231,19 @@
       <c r="F27" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="130"/>
-      <c r="B28" s="36" t="s">
+      <c r="G27" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A28" s="129"/>
+      <c r="B28" s="35" t="s">
         <v>44</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="118" t="s">
+      <c r="D28" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="7" t="s">
@@ -2153,16 +2252,19 @@
       <c r="F28" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="130"/>
-      <c r="B29" s="35" t="s">
+      <c r="G28" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A29" s="129"/>
+      <c r="B29" s="34" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="118" t="s">
+      <c r="D29" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="7" t="s">
@@ -2171,16 +2273,19 @@
       <c r="F29" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="130"/>
-      <c r="B30" s="35" t="s">
+      <c r="G29" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A30" s="129"/>
+      <c r="B30" s="34" t="s">
         <v>46</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="118" t="s">
+      <c r="D30" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E30" s="7" t="s">
@@ -2189,16 +2294,19 @@
       <c r="F30" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="130"/>
-      <c r="B31" s="35" t="s">
+      <c r="G30" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A31" s="129"/>
+      <c r="B31" s="34" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="118" t="s">
+      <c r="D31" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E31" s="7" t="s">
@@ -2207,16 +2315,19 @@
       <c r="F31" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="130"/>
-      <c r="B32" s="35" t="s">
+      <c r="G31" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A32" s="129"/>
+      <c r="B32" s="34" t="s">
         <v>48</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D32" s="118" t="s">
+      <c r="D32" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E32" s="7" t="s">
@@ -2225,16 +2336,19 @@
       <c r="F32" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="130"/>
-      <c r="B33" s="35" t="s">
+      <c r="G32" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A33" s="129"/>
+      <c r="B33" s="34" t="s">
         <v>49</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D33" s="118" t="s">
+      <c r="D33" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E33" s="7" t="s">
@@ -2243,16 +2357,19 @@
       <c r="F33" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="130"/>
-      <c r="B34" s="35" t="s">
+      <c r="G33" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A34" s="129"/>
+      <c r="B34" s="34" t="s">
         <v>50</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D34" s="118" t="s">
+      <c r="D34" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="7" t="s">
@@ -2261,16 +2378,19 @@
       <c r="F34" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="130"/>
-      <c r="B35" s="35" t="s">
+      <c r="G34" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A35" s="129"/>
+      <c r="B35" s="34" t="s">
         <v>51</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D35" s="118" t="s">
+      <c r="D35" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E35" s="7" t="s">
@@ -2279,16 +2399,19 @@
       <c r="F35" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="130"/>
-      <c r="B36" s="35" t="s">
+      <c r="G35" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A36" s="129"/>
+      <c r="B36" s="34" t="s">
         <v>52</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="118" t="s">
+      <c r="D36" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E36" s="7" t="s">
@@ -2297,16 +2420,19 @@
       <c r="F36" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="130"/>
-      <c r="B37" s="35" t="s">
+      <c r="G36" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A37" s="129"/>
+      <c r="B37" s="34" t="s">
         <v>53</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="118" t="s">
+      <c r="D37" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="7" t="s">
@@ -2315,16 +2441,19 @@
       <c r="F37" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="130"/>
-      <c r="B38" s="35" t="s">
+      <c r="G37" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A38" s="129"/>
+      <c r="B38" s="34" t="s">
         <v>54</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D38" s="118" t="s">
+      <c r="D38" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E38" s="7" t="s">
@@ -2333,16 +2462,19 @@
       <c r="F38" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="130"/>
-      <c r="B39" s="35" t="s">
+      <c r="G38" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A39" s="129"/>
+      <c r="B39" s="34" t="s">
         <v>55</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D39" s="118" t="s">
+      <c r="D39" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E39" s="7" t="s">
@@ -2351,16 +2483,19 @@
       <c r="F39" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="130"/>
-      <c r="B40" s="35" t="s">
+      <c r="G39" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A40" s="129"/>
+      <c r="B40" s="34" t="s">
         <v>56</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D40" s="118" t="s">
+      <c r="D40" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E40" s="7" t="s">
@@ -2369,16 +2504,19 @@
       <c r="F40" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="130"/>
-      <c r="B41" s="35" t="s">
+      <c r="G40" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A41" s="129"/>
+      <c r="B41" s="34" t="s">
         <v>57</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D41" s="118" t="s">
+      <c r="D41" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E41" s="7" t="s">
@@ -2387,16 +2525,19 @@
       <c r="F41" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="130"/>
-      <c r="B42" s="36" t="s">
+      <c r="G41" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A42" s="129"/>
+      <c r="B42" s="35" t="s">
         <v>58</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D42" s="118" t="s">
+      <c r="D42" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E42" s="7" t="s">
@@ -2405,16 +2546,19 @@
       <c r="F42" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="130"/>
-      <c r="B43" s="35" t="s">
+      <c r="G42" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A43" s="129"/>
+      <c r="B43" s="34" t="s">
         <v>59</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="118" t="s">
+      <c r="D43" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E43" s="7" t="s">
@@ -2423,16 +2567,19 @@
       <c r="F43" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="130"/>
-      <c r="B44" s="35" t="s">
+      <c r="G43" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A44" s="129"/>
+      <c r="B44" s="34" t="s">
         <v>60</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D44" s="118" t="s">
+      <c r="D44" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E44" s="7" t="s">
@@ -2441,16 +2588,19 @@
       <c r="F44" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="130"/>
-      <c r="B45" s="35" t="s">
+      <c r="G44" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A45" s="129"/>
+      <c r="B45" s="34" t="s">
         <v>61</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D45" s="118" t="s">
+      <c r="D45" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E45" s="7" t="s">
@@ -2459,16 +2609,19 @@
       <c r="F45" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="130"/>
-      <c r="B46" s="35" t="s">
+      <c r="G45" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A46" s="129"/>
+      <c r="B46" s="34" t="s">
         <v>62</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D46" s="118" t="s">
+      <c r="D46" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E46" s="7" t="s">
@@ -2477,16 +2630,19 @@
       <c r="F46" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="130"/>
-      <c r="B47" s="35" t="s">
+      <c r="G46" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A47" s="129"/>
+      <c r="B47" s="34" t="s">
         <v>63</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D47" s="118" t="s">
+      <c r="D47" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E47" s="7" t="s">
@@ -2495,16 +2651,19 @@
       <c r="F47" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="130"/>
-      <c r="B48" s="35" t="s">
+      <c r="G47" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A48" s="129"/>
+      <c r="B48" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D48" s="118" t="s">
+      <c r="D48" s="117" t="s">
         <v>8</v>
       </c>
       <c r="E48" s="7" t="s">
@@ -2513,34 +2672,40 @@
       <c r="F48" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="130"/>
-      <c r="B49" s="37" t="s">
+      <c r="G48" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A49" s="129"/>
+      <c r="B49" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="C49" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="120" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" s="25" t="s">
+      <c r="C49" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="119" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" s="24" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="130"/>
-      <c r="B50" s="38" t="s">
+      <c r="G49" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A50" s="129"/>
+      <c r="B50" s="37" t="s">
         <v>66</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D50" s="121" t="s">
+      <c r="D50" s="120" t="s">
         <v>8</v>
       </c>
       <c r="E50" s="10" t="s">
@@ -2549,58 +2714,65 @@
       <c r="F50" s="9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="131"/>
-      <c r="B51" s="39" t="s">
+      <c r="G50" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A51" s="130"/>
+      <c r="B51" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C51" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="122" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" s="28" t="s">
+      <c r="C51" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" s="27" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" s="46" customFormat="1"/>
-    <row r="53" spans="1:6" s="46" customFormat="1"/>
-    <row r="54" spans="1:6" s="46" customFormat="1"/>
-    <row r="55" spans="1:6" s="46" customFormat="1"/>
-    <row r="56" spans="1:6" s="46" customFormat="1"/>
-    <row r="57" spans="1:6" s="46" customFormat="1"/>
-    <row r="58" spans="1:6" s="46" customFormat="1"/>
-    <row r="59" spans="1:6" s="46" customFormat="1"/>
-    <row r="60" spans="1:6" s="46" customFormat="1"/>
-    <row r="61" spans="1:6" s="46" customFormat="1"/>
-    <row r="62" spans="1:6" s="46" customFormat="1"/>
-    <row r="63" spans="1:6" s="46" customFormat="1"/>
-    <row r="64" spans="1:6" s="46" customFormat="1"/>
-    <row r="65" s="46" customFormat="1"/>
-    <row r="66" s="46" customFormat="1"/>
-    <row r="67" s="46" customFormat="1"/>
-    <row r="68" s="46" customFormat="1"/>
-    <row r="69" s="46" customFormat="1"/>
-    <row r="70" s="46" customFormat="1"/>
-    <row r="71" s="46" customFormat="1"/>
-    <row r="72" s="46" customFormat="1"/>
-    <row r="73" s="46" customFormat="1"/>
-    <row r="74" s="46" customFormat="1"/>
-    <row r="75" s="46" customFormat="1"/>
-    <row r="76" s="46" customFormat="1"/>
-    <row r="77" s="46" customFormat="1"/>
-    <row r="78" s="46" customFormat="1"/>
+      <c r="G51" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" s="45" customFormat="1"/>
+    <row r="53" spans="1:7" s="45" customFormat="1"/>
+    <row r="54" spans="1:7" s="45" customFormat="1"/>
+    <row r="55" spans="1:7" s="45" customFormat="1"/>
+    <row r="56" spans="1:7" s="45" customFormat="1"/>
+    <row r="57" spans="1:7" s="45" customFormat="1"/>
+    <row r="58" spans="1:7" s="45" customFormat="1"/>
+    <row r="59" spans="1:7" s="45" customFormat="1"/>
+    <row r="60" spans="1:7" s="45" customFormat="1"/>
+    <row r="61" spans="1:7" s="45" customFormat="1"/>
+    <row r="62" spans="1:7" s="45" customFormat="1"/>
+    <row r="63" spans="1:7" s="45" customFormat="1"/>
+    <row r="64" spans="1:7" s="45" customFormat="1"/>
+    <row r="65" s="45" customFormat="1"/>
+    <row r="66" s="45" customFormat="1"/>
+    <row r="67" s="45" customFormat="1"/>
+    <row r="68" s="45" customFormat="1"/>
+    <row r="69" s="45" customFormat="1"/>
+    <row r="70" s="45" customFormat="1"/>
+    <row r="71" s="45" customFormat="1"/>
+    <row r="72" s="45" customFormat="1"/>
+    <row r="73" s="45" customFormat="1"/>
+    <row r="74" s="45" customFormat="1"/>
+    <row r="75" s="45" customFormat="1"/>
+    <row r="76" s="45" customFormat="1"/>
+    <row r="77" s="45" customFormat="1"/>
+    <row r="78" s="45" customFormat="1"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A3:A19"/>
     <mergeCell ref="A20:A51"/>
+    <mergeCell ref="G1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2609,7 +2781,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{063788B7-3269-46D0-9D28-22694C6DFEE2}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
@@ -2620,360 +2792,360 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="77">
+      <c r="A1" s="76">
         <v>202620</v>
       </c>
-      <c r="C1" s="137" t="s">
+      <c r="C1" s="131" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="138"/>
-      <c r="E1" s="139" t="s">
+      <c r="D1" s="132"/>
+      <c r="E1" s="133" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="139"/>
+      <c r="F1" s="133"/>
     </row>
     <row r="2" spans="1:6">
       <c r="B2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="52" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="132" t="s">
+      <c r="A3" s="134" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="55" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="54" t="s">
+      <c r="D3" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="54" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="133"/>
-      <c r="B4" s="79" t="s">
+      <c r="A4" s="135"/>
+      <c r="B4" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="57" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="58" t="s">
+      <c r="C4" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="59" t="s">
+      <c r="F4" s="58" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="133"/>
-      <c r="B5" s="79" t="s">
+      <c r="A5" s="135"/>
+      <c r="B5" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="59" t="s">
+      <c r="D5" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="58" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="59" t="s">
+      <c r="E5" s="57" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="58" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="133"/>
-      <c r="B6" s="79" t="s">
+      <c r="A6" s="135"/>
+      <c r="B6" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="58" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="59" t="s">
+      <c r="E6" s="57" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="58" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="133"/>
-      <c r="B7" s="80" t="s">
+      <c r="A7" s="135"/>
+      <c r="B7" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="61" t="s">
+      <c r="C7" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="60" t="s">
+      <c r="D7" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="60" t="s">
+      <c r="E7" s="60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="59" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="133"/>
-      <c r="B8" s="81" t="s">
+      <c r="A8" s="135"/>
+      <c r="B8" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="62" t="s">
+      <c r="C8" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="63" t="s">
+      <c r="D8" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="63" t="s">
+      <c r="E8" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="62" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="133"/>
-      <c r="B9" s="82" t="s">
+      <c r="A9" s="135"/>
+      <c r="B9" s="81" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="65" t="s">
+      <c r="C9" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="66" t="s">
+      <c r="D9" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="67" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="66" t="s">
+      <c r="E9" s="66" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="65" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="134" t="s">
+      <c r="A10" s="136" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="68" t="s">
+      <c r="C10" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="69" t="s">
+      <c r="D10" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="69" t="s">
+      <c r="F10" s="68" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="135"/>
-      <c r="B11" s="84" t="s">
+      <c r="A11" s="137"/>
+      <c r="B11" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="71" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="72" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="71" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="72" t="s">
+      <c r="C11" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="71" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="71" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="135"/>
-      <c r="B12" s="85" t="s">
+      <c r="A12" s="137"/>
+      <c r="B12" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="C12" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="73" t="s">
+      <c r="D12" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="73" t="s">
+      <c r="E12" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="F12" s="73" t="s">
+      <c r="F12" s="72" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="135"/>
-      <c r="B13" s="85" t="s">
+      <c r="A13" s="137"/>
+      <c r="B13" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="73" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="74" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="73" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="74" t="s">
+      <c r="C13" s="72" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="73" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="72" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="73" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="135"/>
-      <c r="B14" s="86" t="s">
+      <c r="A14" s="137"/>
+      <c r="B14" s="85" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="73" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="74" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="73" t="s">
+      <c r="C14" s="72" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="73" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="74" t="s">
+      <c r="F14" s="73" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="135"/>
-      <c r="B15" s="85" t="s">
+      <c r="A15" s="137"/>
+      <c r="B15" s="84" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="73" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="74" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="73" t="s">
+      <c r="C15" s="72" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="73" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="74" t="s">
+      <c r="F15" s="73" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="135"/>
-      <c r="B16" s="85" t="s">
+      <c r="A16" s="137"/>
+      <c r="B16" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="73" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="74" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="73" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="74" t="s">
+      <c r="C16" s="72" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="73" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="72" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="73" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="135"/>
-      <c r="B17" s="85" t="s">
+      <c r="A17" s="137"/>
+      <c r="B17" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="73" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="74" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="73" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="74" t="s">
+      <c r="C17" s="72" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="73" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="72" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="73" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="135"/>
-      <c r="B18" s="85" t="s">
+      <c r="A18" s="137"/>
+      <c r="B18" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="73" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="74" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="73" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="74" t="s">
+      <c r="C18" s="72" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="73" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="72" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="73" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="135"/>
-      <c r="B19" s="87" t="s">
+      <c r="A19" s="137"/>
+      <c r="B19" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="76" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="76" t="s">
+      <c r="C19" s="74" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="74" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="75" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="136"/>
-      <c r="B20" s="88" t="s">
+      <c r="A20" s="138"/>
+      <c r="B20" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="89" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="90" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="90" t="s">
+      <c r="C20" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="89" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2991,347 +3163,347 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFADCC9F-F28C-4FAF-800E-D723F2281A00}">
   <dimension ref="A2:H62"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="70.28515625" customWidth="1"/>
-    <col min="3" max="3" width="79.28515625" style="46" customWidth="1"/>
-    <col min="4" max="8" width="9.140625" style="46"/>
+    <col min="3" max="3" width="79.28515625" style="45" customWidth="1"/>
+    <col min="4" max="8" width="9.140625" style="45"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:3">
-      <c r="B2" s="98" t="s">
+      <c r="B2" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="91" t="s">
+      <c r="C2" s="90" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1">
-      <c r="A3" s="129" t="s">
+      <c r="A3" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="92" t="s">
+      <c r="C3" s="91" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
-      <c r="A4" s="130"/>
-      <c r="B4" s="99" t="s">
+      <c r="A4" s="129"/>
+      <c r="B4" s="98" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="92" t="s">
+      <c r="C4" s="91" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
-      <c r="A5" s="130"/>
-      <c r="B5" s="99" t="s">
+      <c r="A5" s="129"/>
+      <c r="B5" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="92" t="s">
+      <c r="C5" s="91" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
-      <c r="A6" s="130"/>
-      <c r="B6" s="100" t="s">
+      <c r="A6" s="129"/>
+      <c r="B6" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="93" t="s">
+      <c r="C6" s="92" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
-      <c r="A7" s="130"/>
-      <c r="B7" s="100" t="s">
+      <c r="A7" s="129"/>
+      <c r="B7" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="93" t="s">
+      <c r="C7" s="92" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
-      <c r="A8" s="130"/>
-      <c r="B8" s="100" t="s">
+      <c r="A8" s="129"/>
+      <c r="B8" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="93" t="s">
+      <c r="C8" s="92" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
-      <c r="A9" s="130"/>
-      <c r="B9" s="100" t="s">
+      <c r="A9" s="129"/>
+      <c r="B9" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="93" t="s">
+      <c r="C9" s="92" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
-      <c r="A10" s="130"/>
-      <c r="B10" s="101" t="s">
+      <c r="A10" s="129"/>
+      <c r="B10" s="100" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="94" t="s">
+      <c r="C10" s="93" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
-      <c r="A11" s="130"/>
-      <c r="B11" s="101" t="s">
+      <c r="A11" s="129"/>
+      <c r="B11" s="100" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="94" t="s">
+      <c r="C11" s="93" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
-      <c r="A12" s="130"/>
-      <c r="B12" s="101" t="s">
+      <c r="A12" s="129"/>
+      <c r="B12" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="94" t="s">
+      <c r="C12" s="93" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1">
-      <c r="A13" s="130"/>
-      <c r="B13" s="100" t="s">
+      <c r="A13" s="129"/>
+      <c r="B13" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="93" t="s">
+      <c r="C13" s="92" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1">
-      <c r="A14" s="130"/>
-      <c r="B14" s="100" t="s">
+      <c r="A14" s="129"/>
+      <c r="B14" s="99" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="93" t="s">
+      <c r="C14" s="92" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1">
-      <c r="A15" s="130"/>
-      <c r="B15" s="100" t="s">
+      <c r="A15" s="129"/>
+      <c r="B15" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="93" t="s">
+      <c r="C15" s="92" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1">
-      <c r="A16" s="130"/>
-      <c r="B16" s="100" t="s">
+      <c r="A16" s="129"/>
+      <c r="B16" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="93" t="s">
+      <c r="C16" s="92" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1">
-      <c r="A17" s="130"/>
-      <c r="B17" s="100" t="s">
+      <c r="A17" s="129"/>
+      <c r="B17" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="93" t="s">
+      <c r="C17" s="92" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1">
-      <c r="A18" s="130"/>
-      <c r="B18" s="100" t="s">
+      <c r="A18" s="129"/>
+      <c r="B18" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="93" t="s">
+      <c r="C18" s="92" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1">
-      <c r="A19" s="130"/>
-      <c r="B19" s="100" t="s">
+      <c r="A19" s="129"/>
+      <c r="B19" s="99" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="93" t="s">
+      <c r="C19" s="92" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1">
-      <c r="A20" s="130"/>
-      <c r="B20" s="100" t="s">
+      <c r="A20" s="129"/>
+      <c r="B20" s="99" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="93" t="s">
+      <c r="C20" s="92" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1">
-      <c r="A21" s="130"/>
-      <c r="B21" s="100" t="s">
+      <c r="A21" s="129"/>
+      <c r="B21" s="99" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="93" t="s">
+      <c r="C21" s="92" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" customHeight="1">
-      <c r="A22" s="130"/>
-      <c r="B22" s="100" t="s">
+      <c r="A22" s="129"/>
+      <c r="B22" s="99" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="93" t="s">
+      <c r="C22" s="92" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15" customHeight="1">
-      <c r="A23" s="130"/>
-      <c r="B23" s="100" t="s">
+      <c r="A23" s="129"/>
+      <c r="B23" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="93" t="s">
+      <c r="C23" s="92" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1">
-      <c r="A24" s="130"/>
-      <c r="B24" s="100" t="s">
+      <c r="A24" s="129"/>
+      <c r="B24" s="99" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="93" t="s">
+      <c r="C24" s="92" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1">
-      <c r="A25" s="130"/>
-      <c r="B25" s="100" t="s">
+      <c r="A25" s="129"/>
+      <c r="B25" s="99" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="93" t="s">
+      <c r="C25" s="92" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1">
-      <c r="A26" s="130"/>
-      <c r="B26" s="101" t="s">
+      <c r="A26" s="129"/>
+      <c r="B26" s="100" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="94" t="s">
+      <c r="C26" s="93" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1">
-      <c r="A27" s="130"/>
-      <c r="B27" s="100" t="s">
+      <c r="A27" s="129"/>
+      <c r="B27" s="99" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="93" t="s">
+      <c r="C27" s="92" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1">
-      <c r="A28" s="130"/>
-      <c r="B28" s="100" t="s">
+      <c r="A28" s="129"/>
+      <c r="B28" s="99" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="93" t="s">
+      <c r="C28" s="92" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1">
-      <c r="A29" s="130"/>
-      <c r="B29" s="100" t="s">
+      <c r="A29" s="129"/>
+      <c r="B29" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="93" t="s">
+      <c r="C29" s="92" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1">
-      <c r="A30" s="130"/>
-      <c r="B30" s="100" t="s">
+      <c r="A30" s="129"/>
+      <c r="B30" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="93" t="s">
+      <c r="C30" s="92" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15" customHeight="1">
-      <c r="A31" s="130"/>
-      <c r="B31" s="100" t="s">
+      <c r="A31" s="129"/>
+      <c r="B31" s="99" t="s">
         <v>63</v>
       </c>
-      <c r="C31" s="93" t="s">
+      <c r="C31" s="92" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1">
-      <c r="A32" s="130"/>
-      <c r="B32" s="100" t="s">
+      <c r="A32" s="129"/>
+      <c r="B32" s="99" t="s">
         <v>64</v>
       </c>
-      <c r="C32" s="93" t="s">
+      <c r="C32" s="92" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1">
-      <c r="A33" s="130"/>
-      <c r="B33" s="102" t="s">
+      <c r="A33" s="129"/>
+      <c r="B33" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="95" t="s">
+      <c r="C33" s="94" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1">
-      <c r="A34" s="130"/>
-      <c r="B34" s="103" t="s">
+      <c r="A34" s="129"/>
+      <c r="B34" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="96" t="s">
+      <c r="C34" s="95" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15" customHeight="1">
-      <c r="A35" s="131"/>
-      <c r="B35" s="104" t="s">
+      <c r="A35" s="130"/>
+      <c r="B35" s="103" t="s">
         <v>67</v>
       </c>
-      <c r="C35" s="97" t="s">
+      <c r="C35" s="96" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="46" customFormat="1"/>
-    <row r="37" spans="1:3" s="46" customFormat="1"/>
-    <row r="38" spans="1:3" s="46" customFormat="1"/>
-    <row r="39" spans="1:3" s="46" customFormat="1"/>
-    <row r="40" spans="1:3" s="46" customFormat="1"/>
-    <row r="41" spans="1:3" s="46" customFormat="1"/>
-    <row r="42" spans="1:3" s="46" customFormat="1"/>
-    <row r="43" spans="1:3" s="46" customFormat="1"/>
-    <row r="44" spans="1:3" s="46" customFormat="1"/>
-    <row r="45" spans="1:3" s="46" customFormat="1"/>
-    <row r="46" spans="1:3" s="46" customFormat="1"/>
-    <row r="47" spans="1:3" s="46" customFormat="1"/>
-    <row r="48" spans="1:3" s="46" customFormat="1"/>
-    <row r="49" s="46" customFormat="1"/>
-    <row r="50" s="46" customFormat="1"/>
-    <row r="51" s="46" customFormat="1"/>
-    <row r="52" s="46" customFormat="1"/>
-    <row r="53" s="46" customFormat="1"/>
-    <row r="54" s="46" customFormat="1"/>
-    <row r="55" s="46" customFormat="1"/>
-    <row r="56" s="46" customFormat="1"/>
-    <row r="57" s="46" customFormat="1"/>
-    <row r="58" s="46" customFormat="1"/>
-    <row r="59" s="46" customFormat="1"/>
-    <row r="60" s="46" customFormat="1"/>
-    <row r="61" s="46" customFormat="1"/>
-    <row r="62" s="46" customFormat="1"/>
+    <row r="36" spans="1:3" s="45" customFormat="1"/>
+    <row r="37" spans="1:3" s="45" customFormat="1"/>
+    <row r="38" spans="1:3" s="45" customFormat="1"/>
+    <row r="39" spans="1:3" s="45" customFormat="1"/>
+    <row r="40" spans="1:3" s="45" customFormat="1"/>
+    <row r="41" spans="1:3" s="45" customFormat="1"/>
+    <row r="42" spans="1:3" s="45" customFormat="1"/>
+    <row r="43" spans="1:3" s="45" customFormat="1"/>
+    <row r="44" spans="1:3" s="45" customFormat="1"/>
+    <row r="45" spans="1:3" s="45" customFormat="1"/>
+    <row r="46" spans="1:3" s="45" customFormat="1"/>
+    <row r="47" spans="1:3" s="45" customFormat="1"/>
+    <row r="48" spans="1:3" s="45" customFormat="1"/>
+    <row r="49" s="45" customFormat="1"/>
+    <row r="50" s="45" customFormat="1"/>
+    <row r="51" s="45" customFormat="1"/>
+    <row r="52" s="45" customFormat="1"/>
+    <row r="53" s="45" customFormat="1"/>
+    <row r="54" s="45" customFormat="1"/>
+    <row r="55" s="45" customFormat="1"/>
+    <row r="56" s="45" customFormat="1"/>
+    <row r="57" s="45" customFormat="1"/>
+    <row r="58" s="45" customFormat="1"/>
+    <row r="59" s="45" customFormat="1"/>
+    <row r="60" s="45" customFormat="1"/>
+    <row r="61" s="45" customFormat="1"/>
+    <row r="62" s="45" customFormat="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A3:A35"/>
@@ -3343,88 +3515,88 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D839618A-3F7F-4E40-8E5D-91E2DE768A18}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
     <col min="2" max="2" width="61.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1">
-      <c r="A1" s="77">
+      <c r="A1" s="76">
         <v>202620</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="134" t="s">
+      <c r="A2" s="136" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="84" t="s">
+      <c r="B2" s="83" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="135"/>
-      <c r="B3" s="84" t="s">
+      <c r="A3" s="137"/>
+      <c r="B3" s="83" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="135"/>
-      <c r="B4" s="84" t="s">
+      <c r="A4" s="137"/>
+      <c r="B4" s="83" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="135"/>
-      <c r="B5" s="85" t="s">
+      <c r="A5" s="137"/>
+      <c r="B5" s="84" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="135"/>
-      <c r="B6" s="85" t="s">
+      <c r="A6" s="137"/>
+      <c r="B6" s="84" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="135"/>
-      <c r="B7" s="86" t="s">
+      <c r="A7" s="137"/>
+      <c r="B7" s="85" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="135"/>
-      <c r="B8" s="85" t="s">
+      <c r="A8" s="137"/>
+      <c r="B8" s="84" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="135"/>
-      <c r="B9" s="85" t="s">
+      <c r="A9" s="137"/>
+      <c r="B9" s="84" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="135"/>
-      <c r="B10" s="85" t="s">
+      <c r="A10" s="137"/>
+      <c r="B10" s="84" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="135"/>
-      <c r="B11" s="85" t="s">
+      <c r="A11" s="137"/>
+      <c r="B11" s="84" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="135"/>
-      <c r="B12" s="87" t="s">
+      <c r="A12" s="137"/>
+      <c r="B12" s="86" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="136"/>
-      <c r="B13" s="88" t="s">
+      <c r="A13" s="138"/>
+      <c r="B13" s="87" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3437,26 +3609,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="835fe311-fcf7-40a8-a04c-f183e0236c02" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5d448864-0c9f-4050-9bad-33728c8fdb1b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B5A0A51CE30A8B4DBCE3DBD2733022AF" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="3bf3c5548640487b43df3182757c37a3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="835fe311-fcf7-40a8-a04c-f183e0236c02" xmlns:ns3="5d448864-0c9f-4050-9bad-33728c8fdb1b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4894dec080bf9275fca43a55ad7f59f7" ns2:_="" ns3:_="">
     <xsd:import namespace="835fe311-fcf7-40a8-a04c-f183e0236c02"/>
@@ -3691,14 +3843,60 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="835fe311-fcf7-40a8-a04c-f183e0236c02" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5d448864-0c9f-4050-9bad-33728c8fdb1b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E27D9327-52B2-427E-BEE4-A5B3053531E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{021B3CCF-4003-4861-83E7-51C1BEB31AFF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="835fe311-fcf7-40a8-a04c-f183e0236c02"/>
+    <ds:schemaRef ds:uri="5d448864-0c9f-4050-9bad-33728c8fdb1b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2536229B-AD3D-4FE8-A6FB-8F918E42D623}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2536229B-AD3D-4FE8-A6FB-8F918E42D623}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="835fe311-fcf7-40a8-a04c-f183e0236c02"/>
+    <ds:schemaRef ds:uri="5d448864-0c9f-4050-9bad-33728c8fdb1b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{021B3CCF-4003-4861-83E7-51C1BEB31AFF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E27D9327-52B2-427E-BEE4-A5B3053531E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>